--- a/www/profiles/profile-Wine-zgpr-500.xlsx
+++ b/www/profiles/profile-Wine-zgpr-500.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\500_AD_Validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\NMRProcFlow\git\RnmrQuant1D\RnmrQuant1D_UI\www\profiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E6FF17-6B61-414D-9CAD-90E03C8FE535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B433CD-F555-4463-80C9-0264989AE557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="120" windowWidth="23016" windowHeight="13584" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
+    <workbookView xWindow="2295" yWindow="2595" windowWidth="21600" windowHeight="11235" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-zgpr-400" sheetId="1" r:id="rId1"/>
@@ -1349,10 +1349,10 @@
         <v>1.1419999999999999</v>
       </c>
       <c r="D36" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5">
         <v>50</v>
